--- a/Result/profitability/2484.xlsx
+++ b/Result/profitability/2484.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.20875</v>
+        <v>0.25375</v>
       </c>
       <c r="N2" t="n">
-        <v>19.3775</v>
+        <v>20.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0.27375</v>
+        <v>0.30375</v>
       </c>
       <c r="N3" t="n">
-        <v>19.4825</v>
+        <v>20.555</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>0.275</v>
+        <v>0.3125</v>
       </c>
       <c r="N4" t="n">
-        <v>20.03625</v>
+        <v>21.1</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2175</v>
+        <v>0.29875</v>
       </c>
       <c r="N5" t="n">
-        <v>18.93125</v>
+        <v>20.15</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="N6" t="n">
-        <v>18.575</v>
+        <v>20.235</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.15125</v>
+        <v>0.17</v>
       </c>
       <c r="N7" t="n">
-        <v>18.1775</v>
+        <v>18.79</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05</v>
+        <v>0.07624999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>17.62</v>
+        <v>18.18375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2484</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>656</v>
+      </c>
+      <c r="D75" t="n">
+        <v>481</v>
+      </c>
+      <c r="E75" t="n">
+        <v>175</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>86</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>106</v>
+      </c>
+      <c r="K75" t="n">
+        <v>86</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.79625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6363636363636365</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.510000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2031531531531532</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.909090909090909</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.5748820754716981</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
